--- a/assets/xlsx/가맹점별투자자산_2026-08-27_2026-08-27.xlsx
+++ b/assets/xlsx/가맹점별투자자산_2026-08-27_2026-08-27.xlsx
@@ -20,7 +20,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,11 +33,6 @@
       <b val="1"/>
       <color rgb="00111827"/>
       <sz val="13"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <color rgb="009CA3AF"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
@@ -101,21 +96,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -481,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20.5" customWidth="1" min="1" max="1"/>
@@ -499,418 +493,404 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>※ 예시값 — 표기 금액·요율·상호는 전부 예시이며 실제 거래 기록이 아니다. 수수료율은 미확정이고 할인율 0.11%는 예정값이다.</t>
-        </is>
-      </c>
-    </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>가맹점</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>투자금액 (원)</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>W금융일수</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>S입금부족율</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Ty수익율</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>비중</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>김성호떡볶이 본점</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="4" t="n">
         <v>312400000</v>
       </c>
-      <c r="C4" s="6" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="D4" s="7" t="n">
+      <c r="C4" s="5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D4" s="6" t="n">
         <v>0.0031</v>
       </c>
-      <c r="E4" s="7" t="n">
-        <v>0.0372</v>
-      </c>
-      <c r="F4" s="8" t="n">
+      <c r="E4" s="6" t="n">
+        <v>0.1295</v>
+      </c>
+      <c r="F4" s="7" t="n">
         <v>0.204</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>달빛곱창 홍대점</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="4" t="n">
         <v>268900000</v>
       </c>
-      <c r="C5" s="6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="D5" s="7" t="n">
+      <c r="C5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="6" t="n">
         <v>0.0055</v>
       </c>
-      <c r="E5" s="7" t="n">
-        <v>0.0349</v>
-      </c>
-      <c r="F5" s="8" t="n">
+      <c r="E5" s="6" t="n">
+        <v>0.1338</v>
+      </c>
+      <c r="F5" s="7" t="n">
         <v>0.177</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>성호분식 2호점</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="4" t="n">
         <v>197300000</v>
       </c>
-      <c r="C6" s="6" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="D6" s="7" t="n">
+      <c r="C6" s="5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D6" s="6" t="n">
         <v>0.0028</v>
       </c>
-      <c r="E6" s="7" t="n">
-        <v>0.0332</v>
-      </c>
-      <c r="F6" s="8" t="n">
+      <c r="E6" s="6" t="n">
+        <v>0.1217</v>
+      </c>
+      <c r="F6" s="7" t="n">
         <v>0.13</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>바다마루 횟집</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="4" t="n">
         <v>152600000</v>
       </c>
-      <c r="C7" s="6" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="D7" s="7" t="n">
+      <c r="C7" s="5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>0.0047</v>
       </c>
-      <c r="E7" s="7" t="n">
-        <v>0.0394</v>
-      </c>
-      <c r="F7" s="8" t="n">
+      <c r="E7" s="6" t="n">
+        <v>0.1434</v>
+      </c>
+      <c r="F7" s="7" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>한강커피 잠원점</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="4" t="n">
         <v>121800000</v>
       </c>
-      <c r="C8" s="6" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="D8" s="7" t="n">
+      <c r="C8" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D8" s="6" t="n">
         <v>0.0062</v>
       </c>
-      <c r="E8" s="7" t="n">
-        <v>0.0337</v>
-      </c>
-      <c r="F8" s="8" t="n">
+      <c r="E8" s="6" t="n">
+        <v>0.1606</v>
+      </c>
+      <c r="F8" s="7" t="n">
         <v>0.08</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>김밥나라</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="4" t="n">
         <v>98200000</v>
       </c>
-      <c r="C9" s="6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="D9" s="7" t="n">
+      <c r="C9" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D9" s="6" t="n">
         <v>0.0019</v>
       </c>
-      <c r="E9" s="7" t="n">
-        <v>0.0382</v>
-      </c>
-      <c r="F9" s="8" t="n">
+      <c r="E9" s="6" t="n">
+        <v>0.1147</v>
+      </c>
+      <c r="F9" s="7" t="n">
         <v>0.064</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>초록치킨 서초점</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="4" t="n">
         <v>76100000</v>
       </c>
-      <c r="C10" s="6" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="D10" s="7" t="n">
+      <c r="C10" s="5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D10" s="6" t="n">
         <v>0.0071</v>
       </c>
-      <c r="E10" s="7" t="n">
-        <v>0.0324</v>
-      </c>
-      <c r="F10" s="8" t="n">
+      <c r="E10" s="6" t="n">
+        <v>0.1057</v>
+      </c>
+      <c r="F10" s="7" t="n">
         <v>0.05</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>골목냉면</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="4" t="n">
         <v>57200000</v>
       </c>
-      <c r="C11" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="D11" s="7" t="n">
+      <c r="C11" s="5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D11" s="6" t="n">
         <v>0.0038</v>
       </c>
-      <c r="E11" s="7" t="n">
-        <v>0.0365</v>
-      </c>
-      <c r="F11" s="8" t="n">
+      <c r="E11" s="6" t="n">
+        <v>0.1295</v>
+      </c>
+      <c r="F11" s="7" t="n">
         <v>0.038</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>청춘포차 신촌점</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="4" t="n">
         <v>48900000</v>
       </c>
-      <c r="C12" s="6" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="D12" s="7" t="n">
+      <c r="C12" s="5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D12" s="6" t="n">
         <v>0.0044</v>
       </c>
-      <c r="E12" s="7" t="n">
-        <v>0.0355</v>
-      </c>
-      <c r="F12" s="8" t="n">
+      <c r="E12" s="6" t="n">
+        <v>0.1384</v>
+      </c>
+      <c r="F12" s="7" t="n">
         <v>0.032</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>왕십리곱창타운</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="4" t="n">
         <v>42300000</v>
       </c>
-      <c r="C13" s="6" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="D13" s="7" t="n">
+      <c r="C13" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" s="6" t="n">
         <v>0.0026</v>
       </c>
-      <c r="E13" s="7" t="n">
-        <v>0.0379</v>
-      </c>
-      <c r="F13" s="8" t="n">
+      <c r="E13" s="6" t="n">
+        <v>0.1338</v>
+      </c>
+      <c r="F13" s="7" t="n">
         <v>0.028</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>소소한밥상</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="4" t="n">
         <v>37600000</v>
       </c>
-      <c r="C14" s="6" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="D14" s="7" t="n">
+      <c r="C14" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" s="6" t="n">
         <v>0.0058</v>
       </c>
-      <c r="E14" s="7" t="n">
-        <v>0.0329</v>
-      </c>
-      <c r="F14" s="8" t="n">
+      <c r="E14" s="6" t="n">
+        <v>0.1004</v>
+      </c>
+      <c r="F14" s="7" t="n">
         <v>0.025</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>대박국수 사당점</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="4" t="n">
         <v>31400000</v>
       </c>
-      <c r="C15" s="6" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="D15" s="7" t="n">
+      <c r="C15" s="5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D15" s="6" t="n">
         <v>0.0033</v>
       </c>
-      <c r="E15" s="7" t="n">
-        <v>0.0343</v>
-      </c>
-      <c r="F15" s="8" t="n">
+      <c r="E15" s="6" t="n">
+        <v>0.1255</v>
+      </c>
+      <c r="F15" s="7" t="n">
         <v>0.021</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>정든수산</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="4" t="n">
         <v>26800000</v>
       </c>
-      <c r="C16" s="6" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="D16" s="7" t="n">
+      <c r="C16" s="5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="D16" s="6" t="n">
         <v>0.0051</v>
       </c>
-      <c r="E16" s="7" t="n">
-        <v>0.0368</v>
-      </c>
-      <c r="F16" s="8" t="n">
+      <c r="E16" s="6" t="n">
+        <v>0.1544</v>
+      </c>
+      <c r="F16" s="7" t="n">
         <v>0.018</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>착한고기 은평점</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="4" t="n">
         <v>21500000</v>
       </c>
-      <c r="C17" s="6" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="D17" s="7" t="n">
+      <c r="C17" s="5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D17" s="6" t="n">
         <v>0.0067</v>
       </c>
-      <c r="E17" s="7" t="n">
-        <v>0.0319</v>
-      </c>
-      <c r="F17" s="8" t="n">
+      <c r="E17" s="6" t="n">
+        <v>0.1384</v>
+      </c>
+      <c r="F17" s="7" t="n">
         <v>0.014</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>커피한잔 마포점</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B18" s="4" t="n">
         <v>17200000</v>
       </c>
-      <c r="C18" s="6" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="D18" s="7" t="n">
+      <c r="C18" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D18" s="6" t="n">
         <v>0.0022</v>
       </c>
-      <c r="E18" s="7" t="n">
-        <v>0.0362</v>
-      </c>
-      <c r="F18" s="8" t="n">
+      <c r="E18" s="6" t="n">
+        <v>0.1673</v>
+      </c>
+      <c r="F18" s="7" t="n">
         <v>0.011</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>우리동네반찬</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="4" t="n">
         <v>12900000</v>
       </c>
-      <c r="C19" s="6" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="D19" s="7" t="n">
+      <c r="C19" s="5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D19" s="6" t="n">
         <v>0.0035</v>
       </c>
-      <c r="E19" s="7" t="n">
-        <v>0.0386</v>
-      </c>
-      <c r="F19" s="8" t="n">
+      <c r="E19" s="6" t="n">
+        <v>0.0854</v>
+      </c>
+      <c r="F19" s="7" t="n">
         <v>0.008</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="B20" s="10" t="n">
+      <c r="B20" s="9" t="n">
         <v>1523100000</v>
       </c>
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="9" t="n"/>
-      <c r="E20" s="9" t="n"/>
-      <c r="F20" s="11" t="n">
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="10" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>※ 비중은 투자실행액 합계(1,523,100,000원) 대비 각 가맹점 투자금액의 구성비.</t>
-        </is>
       </c>
     </row>
   </sheetData>
